--- a/plantillas/Resultados_Opi_Mesa.xlsx
+++ b/plantillas/Resultados_Opi_Mesa.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Visual Studio Code\NodeJS\SIVACC\plantillas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDAAEDF5-C8BB-420D-BC67-5CF26E783E75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BA4E3B-1941-43E2-B6F7-371015698ED1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>Fecha:</t>
-  </si>
-  <si>
-    <t>Hora:</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Distrito</t>
   </si>
@@ -183,7 +177,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -232,6 +226,12 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -573,9 +573,9 @@
       <c r="I2" s="11"/>
       <c r="J2" s="11"/>
     </row>
-    <row r="3" spans="1:10" s="5" customFormat="1" ht="20.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="12"/>
-      <c r="B3" s="12"/>
+    <row r="3" spans="1:10" s="5" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
@@ -631,15 +631,14 @@
       <c r="J7" s="14"/>
     </row>
     <row r="8" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B8" s="9"/>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
       <c r="C8" s="9"/>
       <c r="D8" s="2"/>
       <c r="E8" s="2"/>
       <c r="G8" s="2"/>
-      <c r="I8" s="8" t="s">
-        <v>0</v>
-      </c>
-      <c r="J8" s="7"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="18"/>
     </row>
     <row r="9" spans="1:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B9" s="4"/>
@@ -648,10 +647,8 @@
       <c r="E9" s="4"/>
       <c r="F9" s="4"/>
       <c r="G9" s="4"/>
-      <c r="I9" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="7"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="18"/>
     </row>
     <row r="10" spans="1:10" ht="15" x14ac:dyDescent="0.25">
       <c r="A10" s="13"/>
@@ -667,30 +664,30 @@
     </row>
     <row r="11" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E11" s="10"/>
       <c r="F11" s="10" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="10"/>
       <c r="H11" s="10" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J11" s="10" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
